--- a/src/assets/employees/sondes.xlsx
+++ b/src/assets/employees/sondes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,12 +407,15 @@
         <v>poste</v>
       </c>
       <c r="C1" t="str">
+        <v>projet</v>
+      </c>
+      <c r="D1" t="str">
         <v>tache</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>dureeHeures</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>date</v>
       </c>
     </row>
@@ -429,13 +432,16 @@
       <c r="D2" t="str">
         <v/>
       </c>
-      <c r="E2" t="str">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>